--- a/financial_models/templates/Valuation_v2.02.xlsx
+++ b/financial_models/templates/Valuation_v2.02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04921666-92AD-42E2-B37A-B0B96CD3E905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A7FA8B-80F5-423F-A2A5-DFBDAA0C1F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$69:$F$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$70:$F$70</definedName>
     <definedName name="Common_Shares">Thesis!$C$11</definedName>
     <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$13</definedName>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="319">
   <si>
     <t>HKD</t>
   </si>
@@ -1242,6 +1242,60 @@
   </si>
   <si>
     <t>Unbiased Scenario where the company FCFE has no growth and no risk.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assumption</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>For both Base and Pessimistic case, I would use 10 yrs to do forecast</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lastest</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>WCInv is excluded</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Given </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>六福珠宝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>’s (0590.HK) normalized FCFE of HKD 1,270,672,000, please analyze its valuation assumptions under three scenarios (Base, Pessimistic, Optimistic) using a two-stage model, a growth stage and a terminal stage. Define the growth period, growth rates and probabilities for each scenario. Explain the rationale behind the probabilities. Summarize the business drivers and scenario narratives to align with the model’s inputs. For context only, the terminal value assumes 0% growth to prevent overvaluation. The finalized scenarios will be incorporated directly into the valuation framework.”</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prompt for Scenario Analysis</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Devil's advocate Case</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>There is always a chance the some devil's advocate is right and I'm wrong, so the probabilities should reflect this depending on how illogical this implied drivers are.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1268,7 +1322,7 @@
     <numFmt numFmtId="191" formatCode="0&quot; yrs&quot;"/>
     <numFmt numFmtId="192" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="37" x14ac:knownFonts="1">
+  <fonts count="38" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1543,8 +1597,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1587,8 +1648,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1627,48 +1694,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="226">
+  <cellXfs count="227">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2150,19 +2180,18 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2177,6 +2206,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2225,22 +2261,12 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF0000FF"/>
       <color rgb="FFFF0000"/>
-      <color rgb="FF0000FF"/>
       <color rgb="FF003871"/>
       <color rgb="FF005078"/>
       <color rgb="FF002850"/>
@@ -2898,8 +2924,8 @@
         <v>126</v>
       </c>
       <c r="C69" s="201">
-        <f>Scenarios!F54</f>
-        <v>-0.26242457844765199</v>
+        <f>Scenarios!F71</f>
+        <v>-0.26862203580089039</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
@@ -3006,8 +3032,8 @@
         <v>128</v>
       </c>
       <c r="C90" s="192">
-        <f>Scenarios!C54</f>
-        <v>13.300145698175813</v>
+        <f>Scenarios!C71</f>
+        <v>13.72374374218604</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Reporting_currency</f>
@@ -3056,7 +3082,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D85:D88">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="lessThan">
       <formula>$F$13</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5111,12 +5137,12 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C4:M13 C16:M19 C22:M25 C28:M28 C35:M39 C41:M42 C44:M46 C64:H65 C66:M67">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32:M33 C49:M52">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>ISBLANK(C32)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5922,52 +5948,21 @@
         <v>0</v>
       </c>
       <c r="D16" s="66"/>
-      <c r="E16" s="85"/>
+      <c r="E16" s="85" t="s">
+        <v>314</v>
+      </c>
       <c r="F16" s="66"/>
-      <c r="G16" s="77">
-        <f>Data!C51</f>
-        <v>-626583</v>
-      </c>
-      <c r="H16" s="77">
-        <f>Data!D51</f>
-        <v>-352099</v>
-      </c>
-      <c r="I16" s="77">
-        <f>Data!E51</f>
-        <v>-1045251</v>
-      </c>
-      <c r="J16" s="77">
-        <f>Data!F51</f>
-        <v>818677</v>
-      </c>
-      <c r="K16" s="77">
-        <f>Data!G51</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="77">
-        <f>Data!H51</f>
-        <v>0</v>
-      </c>
-      <c r="M16" s="77" t="str">
-        <f>Data!I51</f>
-        <v/>
-      </c>
-      <c r="N16" s="77" t="str">
-        <f>Data!J51</f>
-        <v/>
-      </c>
-      <c r="O16" s="77" t="str">
-        <f>Data!K51</f>
-        <v/>
-      </c>
-      <c r="P16" s="77" t="str">
-        <f>Data!L51</f>
-        <v/>
-      </c>
-      <c r="Q16" s="77" t="str">
-        <f>Data!M51</f>
-        <v/>
-      </c>
+      <c r="G16" s="222"/>
+      <c r="H16" s="222"/>
+      <c r="I16" s="222"/>
+      <c r="J16" s="222"/>
+      <c r="K16" s="222"/>
+      <c r="L16" s="222"/>
+      <c r="M16" s="222"/>
+      <c r="N16" s="222"/>
+      <c r="O16" s="222"/>
+      <c r="P16" s="222"/>
+      <c r="Q16" s="222"/>
     </row>
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="12"/>
@@ -6008,19 +6003,19 @@
       <c r="F18" s="66"/>
       <c r="G18" s="80">
         <f>IF(G$4="","",SUM(G15:G17))</f>
-        <v>679442</v>
+        <v>1306025</v>
       </c>
       <c r="H18" s="80">
         <f t="shared" ref="H18:Q18" si="8">IF(H$4="","",SUM(H15:H17))</f>
-        <v>1006925</v>
+        <v>1359024</v>
       </c>
       <c r="I18" s="80">
         <f t="shared" si="8"/>
-        <v>126605</v>
+        <v>1171856</v>
       </c>
       <c r="J18" s="80">
         <f t="shared" si="8"/>
-        <v>1934910</v>
+        <v>1116233</v>
       </c>
       <c r="K18" s="80">
         <f t="shared" si="8"/>
@@ -6124,19 +6119,19 @@
       <c r="F20" s="30"/>
       <c r="G20" s="68">
         <f>IF(G$4="","",G18+G19)</f>
-        <v>927759</v>
+        <v>1554342</v>
       </c>
       <c r="H20" s="68">
         <f t="shared" ref="H20:Q20" si="9">IF(H$4="","",H18+H19)</f>
-        <v>1197102</v>
+        <v>1549201</v>
       </c>
       <c r="I20" s="68">
         <f t="shared" si="9"/>
-        <v>327302</v>
+        <v>1372553</v>
       </c>
       <c r="J20" s="68">
         <f t="shared" si="9"/>
-        <v>2216164</v>
+        <v>1397487</v>
       </c>
       <c r="K20" s="68">
         <f t="shared" si="9"/>
@@ -6795,19 +6790,19 @@
       <c r="F33" s="30"/>
       <c r="G33" s="8">
         <f t="shared" ref="G33:Q33" si="21">IF(G$4="","",-G16/G$4)</f>
-        <v>4.0883763120383568E-2</v>
+        <v>0</v>
       </c>
       <c r="H33" s="8">
         <f t="shared" si="21"/>
-        <v>2.9395857885609465E-2</v>
+        <v>0</v>
       </c>
       <c r="I33" s="8">
         <f t="shared" si="21"/>
-        <v>8.9049969572670459E-2</v>
+        <v>0</v>
       </c>
       <c r="J33" s="8">
         <f t="shared" si="21"/>
-        <v>-9.2387546571707307E-2</v>
+        <v>0</v>
       </c>
       <c r="K33" s="8">
         <f t="shared" si="21"/>
@@ -6909,19 +6904,19 @@
       <c r="F35" s="99"/>
       <c r="G35" s="79">
         <f t="shared" ref="G35:Q35" si="23">IF(G$4="","",ABS(G20/G$4))</f>
-        <v>6.0535123341686481E-2</v>
+        <v>0.10141888646207005</v>
       </c>
       <c r="H35" s="79">
         <f t="shared" si="23"/>
-        <v>9.9943028144297091E-2</v>
+        <v>0.12933888602990656</v>
       </c>
       <c r="I35" s="79">
         <f t="shared" si="23"/>
-        <v>2.7884434591379664E-2</v>
+        <v>0.11693440416405013</v>
       </c>
       <c r="J35" s="79">
         <f t="shared" si="23"/>
-        <v>0.25009369355746058</v>
+        <v>0.15770614698575328</v>
       </c>
       <c r="K35" s="79">
         <f t="shared" si="23"/>
@@ -7067,19 +7062,19 @@
       <c r="F39" s="30"/>
       <c r="G39" s="101">
         <f t="shared" ref="G39:Q39" si="25">IF(G$4="","",G20*$C$3/(Market_Price*Common_Shares))</f>
-        <v>0.10077927517308544</v>
+        <v>0.16884283540346573</v>
       </c>
       <c r="H39" s="101">
         <f t="shared" si="25"/>
-        <v>0.13003708060848876</v>
+        <v>0.16828438622252023</v>
       </c>
       <c r="I39" s="101">
         <f t="shared" si="25"/>
-        <v>3.5553692632139609E-2</v>
+        <v>0.14909572041515518</v>
       </c>
       <c r="J39" s="101">
         <f t="shared" si="25"/>
-        <v>0.24073428722834889</v>
+        <v>0.15180421523672596</v>
       </c>
       <c r="K39" s="101">
         <f t="shared" si="25"/>
@@ -9995,7 +9990,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q9 G11:Q11 G14:Q14 G19:Q19 G47:Q48 G51:Q51">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>ISBLANK(G4)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10718,7 +10713,7 @@
       </c>
       <c r="D47" s="123">
         <f>Normalized_FCF!G18/G19</f>
-        <v>4.8775032000803437E-2</v>
+        <v>9.3755480480820011E-2</v>
       </c>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10757,7 +10752,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H89"/>
+  <dimension ref="B2:H90"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.59765625" customWidth="1"/>
@@ -10881,16 +10876,9 @@
       <c r="F11" s="40"/>
       <c r="H11" s="164"/>
     </row>
-    <row r="12" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B12" s="163" t="s">
         <v>276</v>
-      </c>
-      <c r="E12" s="151" t="s">
-        <v>278</v>
-      </c>
-      <c r="F12" s="200" t="str">
-        <f>"("&amp;D4&amp;")"</f>
-        <v>(HKD)</v>
       </c>
       <c r="H12" s="164"/>
     </row>
@@ -10899,15 +10887,8 @@
         <v>274</v>
       </c>
       <c r="C13" s="211">
-        <f>Scenarios!C22</f>
+        <f>Scenarios!C25</f>
         <v>-3.7999999999999999E-2</v>
-      </c>
-      <c r="E13" s="138" t="s">
-        <v>249</v>
-      </c>
-      <c r="F13">
-        <f>Market_Price</f>
-        <v>15.68</v>
       </c>
       <c r="H13" s="164"/>
     </row>
@@ -10916,11 +10897,8 @@
         <v>275</v>
       </c>
       <c r="C14" s="212">
-        <f>Scenarios!C21</f>
+        <f>Scenarios!C24</f>
         <v>10</v>
-      </c>
-      <c r="E14" s="138" t="s">
-        <v>280</v>
       </c>
       <c r="H14" s="164"/>
     </row>
@@ -10933,11 +10911,8 @@
         <v>15.699957264324397</v>
       </c>
       <c r="D15" t="str">
-        <f>IF(ROUND(C15,1)=ROUND(F13,1),"equals Market Price","a Current Projection")</f>
+        <f>IF(ROUND(C15,1)=ROUND(Scenarios!C29,1),"equals Market Price","a Current Projection")</f>
         <v>equals Market Price</v>
-      </c>
-      <c r="E15" s="138" t="s">
-        <v>277</v>
       </c>
       <c r="H15" s="164"/>
     </row>
@@ -11675,20 +11650,20 @@
         <v>11252490.154549377</v>
       </c>
       <c r="C52" s="175">
+        <f>C74</f>
+        <v>-0.15</v>
+      </c>
+      <c r="D52" s="175">
         <f>C73</f>
-        <v>-0.15</v>
-      </c>
-      <c r="D52" s="175">
+        <v>0</v>
+      </c>
+      <c r="E52" s="175">
         <f>C72</f>
-        <v>0</v>
-      </c>
-      <c r="E52" s="175">
+        <v>0.03</v>
+      </c>
+      <c r="F52" s="175">
         <f>C71</f>
-        <v>0.01</v>
-      </c>
-      <c r="F52" s="175">
-        <f>C70</f>
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H52" s="164"/>
     </row>
@@ -11704,10 +11679,10 @@
         <v>12706721.269962028</v>
       </c>
       <c r="E53" s="167">
-        <v>12922692.982327804</v>
+        <v>13365142.580878742</v>
       </c>
       <c r="F53" s="167">
-        <v>13142141.538962446</v>
+        <v>13365142.580878742</v>
       </c>
       <c r="H53" s="164"/>
     </row>
@@ -11722,10 +11697,10 @@
         <v>12706721.269962028</v>
       </c>
       <c r="E54" s="167">
-        <v>13134802.320367645</v>
+        <v>14055351.524803255</v>
       </c>
       <c r="F54" s="167">
-        <v>13583940.944009084</v>
+        <v>14055351.524803255</v>
       </c>
       <c r="H54" s="164"/>
     </row>
@@ -11740,10 +11715,10 @@
         <v>12706721.269962026</v>
       </c>
       <c r="E55" s="167">
-        <v>13368901.948442612</v>
+        <v>14856838.36452163</v>
       </c>
       <c r="F55" s="167">
-        <v>14083969.893871106</v>
+        <v>14856838.36452163</v>
       </c>
       <c r="H55" s="164"/>
     </row>
@@ -11758,10 +11733,10 @@
         <v>12706721.269962026</v>
       </c>
       <c r="E56" s="167">
-        <v>13581082.743169647</v>
+        <v>15622934.15890887</v>
       </c>
       <c r="F56" s="167">
-        <v>14549180.863933826</v>
+        <v>15622934.15890887</v>
       </c>
       <c r="H56" s="164"/>
     </row>
@@ -11776,10 +11751,10 @@
         <v>12706721.269962026</v>
       </c>
       <c r="E57" s="167">
-        <v>13756438.873081338</v>
+        <v>16291844.094064875</v>
       </c>
       <c r="F57" s="167">
-        <v>14944116.610065991</v>
+        <v>16291844.094064875</v>
       </c>
       <c r="H57" s="164"/>
     </row>
@@ -11794,10 +11769,10 @@
         <v>12706721.269962024</v>
       </c>
       <c r="E58" s="167">
-        <v>13893779.935453041</v>
+        <v>16846271.166623656</v>
       </c>
       <c r="F58" s="167">
-        <v>15262060.98258711</v>
+        <v>16846271.166623656</v>
       </c>
       <c r="H58" s="164"/>
     </row>
@@ -11829,68 +11804,67 @@
       </c>
       <c r="E61" s="176">
         <f>E52</f>
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="F61" s="176">
         <f>F52</f>
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H61" s="164"/>
     </row>
     <row r="62" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B62" s="188">
-        <f t="shared" ref="B62:B67" si="3">B53</f>
+        <v>0</v>
+      </c>
+      <c r="C62" s="168">
+        <f>D62</f>
+        <v>18.176897600606146</v>
+      </c>
+      <c r="D62" s="168">
+        <f>E62</f>
+        <v>18.176897600606146</v>
+      </c>
+      <c r="E62" s="186">
+        <f>C9</f>
+        <v>18.176897600606146</v>
+      </c>
+      <c r="F62" s="168">
+        <f>E62</f>
+        <v>18.176897600606146</v>
+      </c>
+      <c r="H62" s="164"/>
+    </row>
+    <row r="63" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B63" s="188">
+        <f t="shared" ref="B63:B68" si="3">B53</f>
         <v>5</v>
       </c>
-      <c r="C62" s="168">
-        <f t="shared" ref="C62:F67" si="4">(C53-$C$7)/Common_Shares*$C$3</f>
+      <c r="C63" s="168">
+        <f t="shared" ref="C63:F68" si="4">(C53-$C$7)/Common_Shares*$C$3</f>
         <v>13.288003893211801</v>
       </c>
-      <c r="D62" s="186">
+      <c r="D63" s="186">
         <f t="shared" si="4"/>
         <v>18.176897600606136</v>
       </c>
-      <c r="E62" s="168">
-        <f t="shared" si="4"/>
-        <v>18.544754566520961</v>
-      </c>
-      <c r="F62" s="168">
-        <f t="shared" si="4"/>
-        <v>18.918533518096286</v>
-      </c>
-      <c r="H62" s="164"/>
-    </row>
-    <row r="63" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B63" s="188">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="C63" s="168">
-        <f t="shared" si="4"/>
-        <v>10.426671104716659</v>
-      </c>
-      <c r="D63" s="168">
-        <f t="shared" si="4"/>
-        <v>18.176897600606136</v>
-      </c>
       <c r="E63" s="168">
         <f t="shared" si="4"/>
-        <v>18.906032887088198</v>
+        <v>19.298363291989268</v>
       </c>
       <c r="F63" s="168">
         <f t="shared" si="4"/>
-        <v>19.671034792004711</v>
+        <v>19.298363291989268</v>
       </c>
       <c r="H63" s="164"/>
     </row>
     <row r="64" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B64" s="188">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C64" s="168">
         <f t="shared" si="4"/>
-        <v>8.1426652256346106</v>
+        <v>10.426671104716659</v>
       </c>
       <c r="D64" s="168">
         <f t="shared" si="4"/>
@@ -11898,22 +11872,22 @@
       </c>
       <c r="E64" s="168">
         <f t="shared" si="4"/>
-        <v>19.304766489568504</v>
+        <v>20.473971732456405</v>
       </c>
       <c r="F64" s="168">
         <f t="shared" si="4"/>
-        <v>20.522716386556755</v>
+        <v>20.473971732456405</v>
       </c>
       <c r="H64" s="164"/>
     </row>
     <row r="65" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B65" s="189">
+      <c r="B65" s="188">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C65" s="168">
         <f t="shared" si="4"/>
-        <v>6.5847010940466664</v>
+        <v>8.1426652256346106</v>
       </c>
       <c r="D65" s="168">
         <f t="shared" si="4"/>
@@ -11921,22 +11895,22 @@
       </c>
       <c r="E65" s="168">
         <f t="shared" si="4"/>
-        <v>19.666166519779367</v>
+        <v>21.83911587031519</v>
       </c>
       <c r="F65" s="168">
         <f t="shared" si="4"/>
-        <v>21.315093749698331</v>
+        <v>21.83911587031519</v>
       </c>
       <c r="H65" s="164"/>
     </row>
     <row r="66" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B66" s="189">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C66" s="168">
         <f t="shared" si="4"/>
-        <v>5.5788187555995172</v>
+        <v>6.5847010940466664</v>
       </c>
       <c r="D66" s="168">
         <f t="shared" si="4"/>
@@ -11944,158 +11918,165 @@
       </c>
       <c r="E66" s="168">
         <f t="shared" si="4"/>
-        <v>19.964844403087675</v>
+        <v>23.14397969454653</v>
       </c>
       <c r="F66" s="168">
         <f t="shared" si="4"/>
-        <v>21.987773813731142</v>
-      </c>
+        <v>23.14397969454653</v>
+      </c>
+      <c r="H66" s="164"/>
     </row>
     <row r="67" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B67" s="189">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C67" s="168">
         <f t="shared" si="4"/>
-        <v>4.9436354472056356</v>
+        <v>5.5788187555995172</v>
       </c>
       <c r="D67" s="168">
         <f t="shared" si="4"/>
-        <v>18.176897600606132</v>
+        <v>18.176897600606136</v>
       </c>
       <c r="E67" s="168">
         <f t="shared" si="4"/>
-        <v>20.198772568707845</v>
+        <v>24.283310287990314</v>
       </c>
       <c r="F67" s="168">
         <f t="shared" si="4"/>
-        <v>22.529317198853857</v>
-      </c>
-    </row>
-    <row r="69" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B69" s="172" t="s">
+        <v>24.283310287990314</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B68" s="189">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="C68" s="168">
+        <f t="shared" si="4"/>
+        <v>4.9436354472056356</v>
+      </c>
+      <c r="D68" s="168">
+        <f t="shared" si="4"/>
+        <v>18.176897600606132</v>
+      </c>
+      <c r="E68" s="168">
+        <f t="shared" si="4"/>
+        <v>25.227646277636481</v>
+      </c>
+      <c r="F68" s="168">
+        <f t="shared" si="4"/>
+        <v>25.227646277636481</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B70" s="172" t="s">
         <v>248</v>
       </c>
-      <c r="C69" s="172" t="s">
+      <c r="C70" s="172" t="s">
         <v>273</v>
       </c>
-      <c r="D69" s="172" t="s">
+      <c r="D70" s="172" t="s">
         <v>242</v>
       </c>
-      <c r="E69" s="173" t="s">
+      <c r="E70" s="173" t="s">
         <v>243</v>
       </c>
-      <c r="F69" s="173" t="s">
+      <c r="F70" s="173" t="s">
         <v>251</v>
-      </c>
-    </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B70" s="171" t="s">
-        <v>245</v>
-      </c>
-      <c r="C70" s="187">
-        <f>Scenarios!C40</f>
-        <v>0.02</v>
-      </c>
-      <c r="D70" s="190">
-        <f>Scenarios!C39</f>
-        <v>10</v>
-      </c>
-      <c r="E70" s="180">
-        <f>INDEX(C$62:F$67, MATCH(D70, B$62:B$67, 0), MATCH(C70, C$61:F$61, 0))</f>
-        <v>19.671034792004711</v>
-      </c>
-      <c r="F70" s="187">
-        <f>Scenarios!C42</f>
-        <v>0.15</v>
-      </c>
-      <c r="H70" s="164" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B71" s="171" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C71" s="187">
-        <f>Scenarios!C28</f>
-        <v>0.01</v>
+        <f>Scenarios!C51</f>
+        <v>0.03</v>
       </c>
       <c r="D71" s="190">
-        <f>Scenarios!C27</f>
+        <f>Scenarios!C50</f>
         <v>10</v>
       </c>
       <c r="E71" s="180">
-        <f>INDEX(C$62:F$67, MATCH(D71, B$62:B$67, 0), MATCH(C71, C$61:F$61, 0))</f>
-        <v>18.906032887088198</v>
-      </c>
-      <c r="F71" s="187">
-        <f>Scenarios!C30</f>
-        <v>0.5</v>
-      </c>
+        <f>INDEX(C$62:F$68, MATCH(D71, B$62:B$68, 0), MATCH(C71, C$61:F$61, 0))</f>
+        <v>20.473971732456405</v>
+      </c>
+      <c r="F71" s="187"/>
       <c r="H71" s="164" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B72" s="171" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C72" s="187">
-        <v>0</v>
+        <f>Scenarios!C39</f>
+        <v>0.03</v>
       </c>
       <c r="D72" s="190">
-        <v>0</v>
+        <f>Scenarios!C38</f>
+        <v>5</v>
       </c>
       <c r="E72" s="180">
-        <f>$C$9</f>
-        <v>18.176897600606146</v>
-      </c>
-      <c r="F72" s="187">
-        <f>Scenarios!C18</f>
-        <v>0.2</v>
-      </c>
+        <f>INDEX(C$62:F$68, MATCH(D72, B$62:B$68, 0), MATCH(C72, C$61:F$61, 0))</f>
+        <v>19.298363291989268</v>
+      </c>
+      <c r="F72" s="187"/>
       <c r="H72" s="164" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B73" s="171" t="s">
+        <v>244</v>
+      </c>
+      <c r="C73" s="187">
+        <f>Scenarios!C45</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="190">
+        <f>Scenarios!C44</f>
+        <v>5</v>
+      </c>
+      <c r="E73" s="180">
+        <f>INDEX(C$62:F$68, MATCH(D73, B$62:B$68, 0), MATCH(C73, C$61:F$61, 0))</f>
+        <v>18.176897600606136</v>
+      </c>
+      <c r="F73" s="187"/>
+    </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B74" s="171" t="s">
         <v>247</v>
       </c>
-      <c r="C73" s="187">
-        <f>Scenarios!C34</f>
+      <c r="C74" s="187">
+        <f>Scenarios!C57</f>
         <v>-0.15</v>
       </c>
-      <c r="D73" s="190">
-        <f>Scenarios!C33</f>
+      <c r="D74" s="190">
+        <f>Scenarios!C56</f>
         <v>5</v>
       </c>
-      <c r="E73" s="180">
-        <f>INDEX(C$62:F$67, MATCH(D73, B$62:B$67, 0), MATCH(C73, C$61:F$61, 0))</f>
+      <c r="E74" s="180">
+        <f>INDEX(C$62:F$68, MATCH(D74, B$62:B$68, 0), MATCH(C74, C$61:F$61, 0))</f>
         <v>13.288003893211801</v>
       </c>
-      <c r="F73" s="187">
-        <f>Scenarios!C36</f>
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B74" s="203" t="str">
-        <f>IF(VLOOKUP("No Growth",B70:E73,4,FALSE)&gt;VLOOKUP("Base",B70:E73,4,FALSE),"Note: the No Growth value being higher than the Base or Optimistic values is unusual.","OK")</f>
+      <c r="F74" s="187"/>
+      <c r="H74" s="164" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B75" s="203" t="str">
+        <f>IF(VLOOKUP("No Growth",B71:E74,4,FALSE)&gt;VLOOKUP("Base",B71:E74,4,FALSE),"Note: the No Growth value being higher than the Base or Optimistic values is unusual.","OK")</f>
         <v>OK</v>
       </c>
-      <c r="C74" s="203"/>
-      <c r="D74" s="203"/>
-      <c r="E74" s="203"/>
-      <c r="F74" s="204" t="str">
-        <f>IF(SUM(F70:F73)=1,"100% - OK",SUM(F70:F73)*100&amp;"% Error")</f>
-        <v>100% - OK</v>
-      </c>
-    </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C87" s="159"/>
+      <c r="C75" s="203"/>
+      <c r="D75" s="203"/>
+      <c r="E75" s="203"/>
+      <c r="F75" s="204"/>
     </row>
     <row r="88" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C88" s="159"/>
@@ -12103,41 +12084,66 @@
     <row r="89" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C89" s="159"/>
     </row>
+    <row r="90" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C90" s="159"/>
+    </row>
   </sheetData>
-  <autoFilter ref="B69:F69" xr:uid="{D3EAD7ED-D484-47B2-9C7C-1D1BCBEAE5A9}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B70:F74">
-      <sortCondition descending="1" ref="E69"/>
+  <autoFilter ref="B70:F70" xr:uid="{D3EAD7ED-D484-47B2-9C7C-1D1BCBEAE5A9}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B71:F75">
+      <sortCondition descending="1" ref="E70"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="29" type="noConversion"/>
   <conditionalFormatting sqref="C18:F47">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C62:F67">
-    <cfRule type="expression" dxfId="1" priority="6">
-      <formula>ISNUMBER(MATCH(C62, $E$70:$E$73, 0))</formula>
+  <conditionalFormatting sqref="C63:F68">
+    <cfRule type="expression" dxfId="2" priority="8">
+      <formula>ISNUMBER(MATCH(C63, $E$71:$E$74, 0))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E70:E73">
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="lessThan">
-      <formula>$F$13</formula>
+  <conditionalFormatting sqref="E62">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>ISNUMBER(MATCH(E62, $E$71:$E$74, 0))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D70:D73 C14" xr:uid="{A06882BF-7451-4B05-ADA9-B8AC5ACC7F23}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{A06882BF-7451-4B05-ADA9-B8AC5ACC7F23}">
       <formula1>$B$53:$B$58</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="10" operator="lessThan" id="{00000000-000E-0000-0400-000007000000}">
+            <xm:f>Scenarios!$C$29</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>E71:E74</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I60"/>
+  <dimension ref="B2:I77"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
@@ -12175,454 +12181,586 @@
     </row>
     <row r="6" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B6" s="209" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="146">
+        <f>Valuation_Model!C3</f>
+        <v>1000</v>
+      </c>
+      <c r="E6" s="138" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B7" s="138" t="s">
+        <v>313</v>
+      </c>
+      <c r="C7" s="158">
+        <f>Normalized_FCF!G20</f>
+        <v>1554342</v>
+      </c>
+      <c r="E7" s="224" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B8" s="138" t="s">
+        <v>136</v>
+      </c>
+      <c r="C8" s="158">
+        <f>Normalized_FCF!C20</f>
+        <v>1270672.1269962033</v>
+      </c>
+      <c r="E8" s="225"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="E9" s="225"/>
+    </row>
+    <row r="10" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B10" s="209" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B7" s="162" t="s">
+      <c r="E10" s="225"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B11" s="162" t="s">
         <v>295</v>
       </c>
-      <c r="C7" s="208">
+      <c r="C11" s="208">
         <f>AVERAGE(Normalized_FCF!G42:INDEX(Normalized_FCF!G42:Q42, $C$4))</f>
         <v>0.10334930065770259</v>
       </c>
-      <c r="D7" s="208"/>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B8" s="193" t="s">
+      <c r="D11" s="208"/>
+      <c r="E11" s="225"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B12" s="193" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B9" s="138" t="s">
+      <c r="E12" s="225"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B13" s="138" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="11" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B11" s="209" t="s">
+      <c r="E13" s="225"/>
+    </row>
+    <row r="15" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B15" s="209" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B12" s="138" t="s">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B16" s="138" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B13" s="193" t="s">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B17" s="193" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="B15" s="39" t="s">
+    <row r="19" spans="2:7" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="B19" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-    </row>
-    <row r="16" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B16" s="209" t="s">
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+    </row>
+    <row r="20" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B20" s="151" t="s">
         <v>302</v>
       </c>
-      <c r="E16" s="209" t="s">
+      <c r="E20" s="209" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B17" s="138" t="s">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B21" s="138" t="s">
         <v>243</v>
       </c>
-      <c r="C17" s="210">
-        <f>Valuation_Model!E72</f>
-        <v>18.176897600606146</v>
-      </c>
-      <c r="D17" t="str">
+      <c r="C21" s="210">
+        <f>Valuation_Model!E73</f>
+        <v>18.176897600606136</v>
+      </c>
+      <c r="D21" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E17" s="225" t="s">
+      <c r="E21" s="221" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B18" s="138" t="s">
-        <v>305</v>
-      </c>
-      <c r="C18" s="215">
-        <v>0.2</v>
-      </c>
-      <c r="D18" s="215"/>
-      <c r="E18" s="221"/>
-    </row>
-    <row r="20" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B20" s="209" t="s">
+    <row r="23" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B23" s="151" t="s">
         <v>301</v>
       </c>
-      <c r="E20" s="209" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B21" s="198" t="s">
+      <c r="E23" s="223"/>
+    </row>
+    <row r="24" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="198" t="s">
         <v>274</v>
       </c>
-      <c r="C21" s="196">
+      <c r="C24" s="196">
         <v>10</v>
       </c>
-      <c r="D21" s="196"/>
-      <c r="E21" s="222"/>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B22" s="162" t="s">
+      <c r="D24" s="196"/>
+      <c r="E24" s="226"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B25" s="162" t="s">
         <v>275</v>
       </c>
-      <c r="C22" s="197">
+      <c r="C25" s="197">
         <v>-3.7999999999999999E-2</v>
       </c>
-      <c r="D22" s="197"/>
-      <c r="E22" s="223"/>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B23" s="138" t="s">
+      <c r="D25" s="197"/>
+      <c r="E25" s="226"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B26" s="138" t="s">
         <v>243</v>
       </c>
-      <c r="C23" s="210">
+      <c r="C26" s="210">
         <f>Valuation_Model!C15</f>
         <v>15.699957264324397</v>
       </c>
-      <c r="D23" s="210"/>
-      <c r="E23" s="224"/>
-    </row>
-    <row r="25" spans="2:7" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="B25" s="39" t="s">
-        <v>304</v>
-      </c>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="40"/>
-    </row>
-    <row r="26" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B26" s="209" t="s">
-        <v>59</v>
-      </c>
-      <c r="E26" s="209" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="198" t="s">
-        <v>274</v>
-      </c>
-      <c r="C27" s="213">
-        <v>10</v>
-      </c>
-      <c r="D27" s="213"/>
-      <c r="E27" s="221"/>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" s="162" t="s">
-        <v>275</v>
-      </c>
-      <c r="C28" s="214">
-        <v>0.01</v>
-      </c>
-      <c r="D28" s="214"/>
-      <c r="E28" s="221"/>
+      <c r="D26" s="210"/>
+      <c r="E26" s="226"/>
+    </row>
+    <row r="28" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B28" s="151" t="s">
+        <v>278</v>
+      </c>
+      <c r="C28" s="200"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B29" s="138" t="s">
-        <v>243</v>
-      </c>
-      <c r="C29" s="210">
-        <f>Valuation_Model!E71</f>
-        <v>18.906032887088198</v>
-      </c>
-      <c r="D29" s="210"/>
-      <c r="E29" s="221"/>
+        <v>249</v>
+      </c>
+      <c r="C29">
+        <f>Market_Price</f>
+        <v>15.68</v>
+      </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B30" s="138" t="s">
+        <v>280</v>
+      </c>
+      <c r="C30">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B31" s="138" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="B33" s="39" t="s">
+        <v>304</v>
+      </c>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+    </row>
+    <row r="34" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B34" s="151" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B35" s="198" t="s">
+        <v>274</v>
+      </c>
+      <c r="C35" s="196">
+        <v>5</v>
+      </c>
+      <c r="E35" s="138" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B37" s="209" t="s">
+        <v>59</v>
+      </c>
+      <c r="E37" s="209" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B38" s="198" t="s">
+        <v>274</v>
+      </c>
+      <c r="C38" s="216">
+        <f>C35</f>
+        <v>5</v>
+      </c>
+      <c r="D38" s="213"/>
+      <c r="E38" s="225"/>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B39" s="162" t="s">
+        <v>275</v>
+      </c>
+      <c r="C39" s="214">
+        <v>0.03</v>
+      </c>
+      <c r="D39" s="214"/>
+      <c r="E39" s="225"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B40" s="138" t="s">
+        <v>243</v>
+      </c>
+      <c r="C40" s="210">
+        <f>Valuation_Model!E72</f>
+        <v>19.298363291989268</v>
+      </c>
+      <c r="D40" s="210"/>
+      <c r="E40" s="225"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B41" s="138" t="s">
         <v>305</v>
       </c>
-      <c r="C30" s="215">
-        <v>0.5</v>
-      </c>
-      <c r="D30" s="215"/>
-      <c r="E30" s="221"/>
-    </row>
-    <row r="32" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B32" s="209" t="s">
+      <c r="C41" s="215">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D41" s="215"/>
+      <c r="E41" s="225"/>
+    </row>
+    <row r="43" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B43" s="209" t="s">
         <v>60</v>
       </c>
-      <c r="E32" s="209" t="s">
+      <c r="E43" s="209" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B33" s="198" t="s">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B44" s="198" t="s">
         <v>274</v>
       </c>
-      <c r="C33" s="213">
+      <c r="C44" s="216">
+        <f>C35</f>
         <v>5</v>
       </c>
-      <c r="D33" s="213"/>
-      <c r="E33" s="221"/>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B34" s="162" t="s">
+      <c r="D44" s="213"/>
+      <c r="E44" s="225"/>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B45" s="162" t="s">
         <v>275</v>
       </c>
-      <c r="C34" s="214">
-        <v>-0.15</v>
-      </c>
-      <c r="D34" s="214"/>
-      <c r="E34" s="221"/>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B35" s="138" t="s">
+      <c r="C45" s="214">
+        <v>0</v>
+      </c>
+      <c r="D45" s="214"/>
+      <c r="E45" s="225"/>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B46" s="138" t="s">
         <v>243</v>
       </c>
-      <c r="C35" s="210">
+      <c r="C46" s="210">
         <f>Valuation_Model!E73</f>
-        <v>13.288003893211801</v>
-      </c>
-      <c r="D35" t="str">
+        <v>18.176897600606136</v>
+      </c>
+      <c r="D46" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E35" s="221"/>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B36" s="138" t="s">
+      <c r="E46" s="225"/>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B47" s="138" t="s">
         <v>305</v>
       </c>
-      <c r="C36" s="215">
+      <c r="C47" s="215">
         <v>0.15</v>
       </c>
-      <c r="D36" s="215"/>
-      <c r="E36" s="221"/>
-    </row>
-    <row r="38" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B38" s="209" t="s">
+      <c r="D47" s="215"/>
+      <c r="E47" s="225"/>
+    </row>
+    <row r="49" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B49" s="209" t="s">
         <v>300</v>
       </c>
-      <c r="E38" s="209" t="s">
+      <c r="E49" s="209" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B39" s="198" t="s">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B50" s="198" t="s">
         <v>274</v>
       </c>
-      <c r="C39" s="213">
+      <c r="C50" s="213">
         <v>10</v>
       </c>
-      <c r="D39" s="213"/>
-      <c r="E39" s="221"/>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B40" s="162" t="s">
+      <c r="D50" s="213"/>
+      <c r="E50" s="225"/>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B51" s="162" t="s">
         <v>275</v>
       </c>
-      <c r="C40" s="214">
-        <v>0.02</v>
-      </c>
-      <c r="D40" s="214"/>
-      <c r="E40" s="221"/>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B41" s="138" t="s">
+      <c r="C51" s="214">
+        <v>0.03</v>
+      </c>
+      <c r="D51" s="214"/>
+      <c r="E51" s="225"/>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B52" s="138" t="s">
         <v>243</v>
       </c>
-      <c r="C41" s="210">
-        <f>Valuation_Model!E70</f>
-        <v>19.671034792004711</v>
-      </c>
-      <c r="D41" t="str">
+      <c r="C52" s="210">
+        <f>Valuation_Model!E71</f>
+        <v>20.473971732456405</v>
+      </c>
+      <c r="D52" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E41" s="221"/>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B42" s="138" t="s">
+      <c r="E52" s="225"/>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B53" s="138" t="s">
         <v>305</v>
       </c>
-      <c r="C42" s="215">
-        <v>0.15</v>
-      </c>
-      <c r="D42" s="215"/>
-      <c r="E42" s="221"/>
-    </row>
-    <row r="44" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B44" s="138" t="s">
-        <v>252</v>
-      </c>
-      <c r="C44" s="202">
-        <f>C18*C17+C30*C29+C36*C35+C42*C41</f>
-        <v>18.032251766447807</v>
-      </c>
-      <c r="D44" t="str">
+      <c r="C53" s="215">
+        <v>0.2</v>
+      </c>
+      <c r="D53" s="215"/>
+      <c r="E53" s="225"/>
+    </row>
+    <row r="55" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B55" s="209" t="s">
+        <v>317</v>
+      </c>
+      <c r="E55" s="209" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B56" s="198" t="s">
+        <v>274</v>
+      </c>
+      <c r="C56" s="216">
+        <f>C35</f>
+        <v>5</v>
+      </c>
+      <c r="D56" s="213"/>
+      <c r="E56" s="224" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B57" s="162" t="s">
+        <v>275</v>
+      </c>
+      <c r="C57" s="197">
+        <v>-0.15</v>
+      </c>
+      <c r="D57" s="214"/>
+      <c r="E57" s="225"/>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B58" s="138" t="s">
+        <v>243</v>
+      </c>
+      <c r="C58" s="210">
+        <f>Valuation_Model!E74</f>
+        <v>13.288003893211801</v>
+      </c>
+      <c r="D58" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-    </row>
-    <row r="46" spans="2:7" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="B46" s="39" t="s">
+      <c r="E58" s="225"/>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B59" s="138" t="s">
+        <v>305</v>
+      </c>
+      <c r="C59" s="218">
+        <f>1-C41-C47-C53</f>
+        <v>9.9999999999999922E-2</v>
+      </c>
+      <c r="D59" s="215"/>
+      <c r="E59" s="225"/>
+    </row>
+    <row r="61" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B61" s="138" t="s">
+        <v>252</v>
+      </c>
+      <c r="C61" s="202">
+        <f>C41*C40+C59*C58+C46*C47+C53*C52</f>
+        <v>18.764229186497477</v>
+      </c>
+      <c r="D61" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="B63" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="C46" s="40"/>
-      <c r="D46" s="40"/>
-      <c r="E46" s="40"/>
-      <c r="F46" s="40"/>
-      <c r="G46" s="40"/>
-    </row>
-    <row r="47" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B47" s="151" t="s">
+      <c r="C63" s="40"/>
+      <c r="D63" s="40"/>
+      <c r="E63" s="40"/>
+      <c r="F63" s="40"/>
+      <c r="G63" s="40"/>
+    </row>
+    <row r="64" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B64" s="151" t="s">
         <v>263</v>
       </c>
-      <c r="E47" s="151" t="s">
+      <c r="E64" s="151" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B48" s="138" t="s">
+    <row r="65" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B65" s="138" t="s">
         <v>281</v>
       </c>
-      <c r="C48" s="218">
+      <c r="C65" s="218">
         <f>Thesis!C68</f>
         <v>0.2</v>
       </c>
-      <c r="D48" s="178"/>
-      <c r="E48" s="138" t="s">
+      <c r="D65" s="178"/>
+      <c r="E65" s="138" t="s">
         <v>264</v>
       </c>
-      <c r="F48" s="216">
+      <c r="F65" s="216">
         <f>Thesis!C67</f>
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B49" s="138" t="s">
+    <row r="66" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B66" s="138" t="s">
         <v>241</v>
       </c>
-      <c r="C49">
+      <c r="C66">
         <f>Normalized_FCF!C91</f>
         <v>1.3599999999999999</v>
       </c>
-      <c r="D49" t="str">
+      <c r="D66" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E49" s="138" t="s">
+      <c r="E66" s="138" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B51" s="151" t="s">
+    <row r="68" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B68" s="151" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B52" s="138" t="s">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B69" s="138" t="s">
         <v>253</v>
       </c>
-      <c r="C52" s="160">
-        <f>PV(C48, F48, -C49, 0)</f>
+      <c r="C69" s="160">
+        <f>PV(C65, F65, -C66, 0)</f>
         <v>2.8648148148148143</v>
       </c>
-      <c r="D52" s="160"/>
-      <c r="E52" s="138"/>
-    </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B53" s="138" t="s">
+      <c r="D69" s="160"/>
+      <c r="E69" s="138"/>
+    </row>
+    <row r="70" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B70" s="138" t="s">
         <v>255</v>
       </c>
-      <c r="C53" s="160">
-        <f>C44/(1+C48)^F48</f>
-        <v>10.435330883360999</v>
-      </c>
-      <c r="D53" s="160"/>
-    </row>
-    <row r="54" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B54" s="153" t="s">
+      <c r="C70" s="160">
+        <f>C61/(1+C65)^F65</f>
+        <v>10.858928927371226</v>
+      </c>
+      <c r="D70" s="160"/>
+    </row>
+    <row r="71" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B71" s="153" t="s">
         <v>229</v>
       </c>
-      <c r="C54" s="154">
-        <f>C52+C53</f>
-        <v>13.300145698175813</v>
-      </c>
-      <c r="D54" t="str">
+      <c r="C71" s="154">
+        <f>C69+C70</f>
+        <v>13.72374374218604</v>
+      </c>
+      <c r="D71" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E54" s="219" t="s">
+      <c r="E71" s="219" t="s">
         <v>267</v>
       </c>
-      <c r="F54" s="220">
-        <f>(C54/C44-1)</f>
-        <v>-0.26242457844765199</v>
-      </c>
-      <c r="I54" s="164" t="s">
+      <c r="F71" s="220">
+        <f>(C71/C61-1)</f>
+        <v>-0.26862203580089039</v>
+      </c>
+      <c r="I71" s="164" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="D57" s="191"/>
-    </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B58" s="124" t="s">
+    <row r="74" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D74" s="191"/>
+    </row>
+    <row r="75" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B75" s="124" t="s">
         <v>53</v>
       </c>
-      <c r="C58" s="125" t="s">
+      <c r="C75" s="125" t="s">
         <v>56</v>
       </c>
-      <c r="D58" s="125" t="s">
+      <c r="D75" s="125" t="s">
         <v>57</v>
       </c>
-      <c r="E58" s="119" t="s">
+      <c r="E75" s="119" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B59" s="9" t="s">
+    <row r="76" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B76" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C59" s="14">
+      <c r="C76" s="14">
         <f>Normalized_FCF!L8</f>
         <v>1617067</v>
       </c>
-      <c r="D59" s="14">
+      <c r="D76" s="14">
         <f>Normalized_FCF!G8</f>
         <v>1876773</v>
       </c>
-      <c r="E59" s="14">
+      <c r="E76" s="14">
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B60" s="9" t="s">
+    <row r="77" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B77" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C60" s="8">
-        <f>(D59/C59)^(1/E59)-1</f>
+      <c r="C77" s="8">
+        <f>(D76/C76)^(1/E76)-1</f>
         <v>2.5133963029188244E-2</v>
       </c>
-      <c r="D60" s="43"/>
-      <c r="E60" s="43"/>
+      <c r="D77" s="43"/>
+      <c r="E77" s="43"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="E27:E30"/>
-    <mergeCell ref="E33:E36"/>
-    <mergeCell ref="E39:E42"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="E17:E18"/>
+  <mergeCells count="6">
+    <mergeCell ref="E50:E53"/>
+    <mergeCell ref="E7:E13"/>
+    <mergeCell ref="E44:E47"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="E38:E41"/>
+    <mergeCell ref="E56:E59"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/templates/Valuation_v2.02.xlsx
+++ b/financial_models/templates/Valuation_v2.02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A7FA8B-80F5-423F-A2A5-DFBDAA0C1F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89ACC8E6-6B24-4271-85C9-D19F702D16C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1261,6 +1261,18 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Prompt for Scenario Analysis</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Devil's advocate Case</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>There is always a chance the some devil's advocate is right and I'm wrong, so the probabilities should reflect this depending on how illogical this implied drivers are.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Given </t>
     </r>
@@ -1272,7 +1284,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>六福珠宝</t>
+      <t>六福珠宝’</t>
     </r>
     <r>
       <rPr>
@@ -1282,20 +1294,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>’s (0590.HK) normalized FCFE of HKD 1,270,672,000, please analyze its valuation assumptions under three scenarios (Base, Pessimistic, Optimistic) using a two-stage model, a growth stage and a terminal stage. Define the growth period, growth rates and probabilities for each scenario. Explain the rationale behind the probabilities. Summarize the business drivers and scenario narratives to align with the model’s inputs. For context only, the terminal value assumes 0% growth to prevent overvaluation. The finalized scenarios will be incorporated directly into the valuation framework.”</t>
+      <t>s (0590.HK) normalized FCFE of HKD 1,270,672,000, please analyze its valuation assumptions under three scenarios (Base, Pessimistic, Optimistic) using a two-stage model, a growth stage and a terminal stage. Define the growth period, growth rates and probabilities for each scenario. Explain the rationale behind the probabilities. Summarize the business drivers and scenario narratives to align with the model’s inputs. For context only, the terminal value assumes 0% growth to prevent overvaluation. The finalized scenarios will be incorporated directly into the valuation framework.”</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prompt for Scenario Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Devil's advocate Case</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>There is always a chance the some devil's advocate is right and I'm wrong, so the probabilities should reflect this depending on how illogical this implied drivers are.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2185,14 +2185,14 @@
     </xf>
     <xf numFmtId="184" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -12188,7 +12188,7 @@
         <v>1000</v>
       </c>
       <c r="E6" s="138" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
@@ -12199,8 +12199,8 @@
         <f>Normalized_FCF!G20</f>
         <v>1554342</v>
       </c>
-      <c r="E7" s="224" t="s">
-        <v>315</v>
+      <c r="E7" s="225" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
@@ -12211,16 +12211,16 @@
         <f>Normalized_FCF!C20</f>
         <v>1270672.1269962033</v>
       </c>
-      <c r="E8" s="225"/>
+      <c r="E8" s="224"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="E9" s="225"/>
+      <c r="E9" s="224"/>
     </row>
     <row r="10" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="209" t="s">
         <v>297</v>
       </c>
-      <c r="E10" s="225"/>
+      <c r="E10" s="224"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="162" t="s">
@@ -12231,19 +12231,19 @@
         <v>0.10334930065770259</v>
       </c>
       <c r="D11" s="208"/>
-      <c r="E11" s="225"/>
+      <c r="E11" s="224"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="193" t="s">
         <v>294</v>
       </c>
-      <c r="E12" s="225"/>
+      <c r="E12" s="224"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="138" t="s">
         <v>175</v>
       </c>
-      <c r="E13" s="225"/>
+      <c r="E13" s="224"/>
     </row>
     <row r="15" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B15" s="209" t="s">
@@ -12402,7 +12402,7 @@
         <v>5</v>
       </c>
       <c r="D38" s="213"/>
-      <c r="E38" s="225"/>
+      <c r="E38" s="224"/>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="162" t="s">
@@ -12412,7 +12412,7 @@
         <v>0.03</v>
       </c>
       <c r="D39" s="214"/>
-      <c r="E39" s="225"/>
+      <c r="E39" s="224"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="138" t="s">
@@ -12423,7 +12423,7 @@
         <v>19.298363291989268</v>
       </c>
       <c r="D40" s="210"/>
-      <c r="E40" s="225"/>
+      <c r="E40" s="224"/>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="138" t="s">
@@ -12433,7 +12433,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D41" s="215"/>
-      <c r="E41" s="225"/>
+      <c r="E41" s="224"/>
     </row>
     <row r="43" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B43" s="209" t="s">
@@ -12452,7 +12452,7 @@
         <v>5</v>
       </c>
       <c r="D44" s="213"/>
-      <c r="E44" s="225"/>
+      <c r="E44" s="224"/>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="162" t="s">
@@ -12462,7 +12462,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="214"/>
-      <c r="E45" s="225"/>
+      <c r="E45" s="224"/>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="138" t="s">
@@ -12476,7 +12476,7 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E46" s="225"/>
+      <c r="E46" s="224"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="138" t="s">
@@ -12486,7 +12486,7 @@
         <v>0.15</v>
       </c>
       <c r="D47" s="215"/>
-      <c r="E47" s="225"/>
+      <c r="E47" s="224"/>
     </row>
     <row r="49" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B49" s="209" t="s">
@@ -12504,7 +12504,7 @@
         <v>10</v>
       </c>
       <c r="D50" s="213"/>
-      <c r="E50" s="225"/>
+      <c r="E50" s="224"/>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B51" s="162" t="s">
@@ -12514,7 +12514,7 @@
         <v>0.03</v>
       </c>
       <c r="D51" s="214"/>
-      <c r="E51" s="225"/>
+      <c r="E51" s="224"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B52" s="138" t="s">
@@ -12528,7 +12528,7 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E52" s="225"/>
+      <c r="E52" s="224"/>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B53" s="138" t="s">
@@ -12538,11 +12538,11 @@
         <v>0.2</v>
       </c>
       <c r="D53" s="215"/>
-      <c r="E53" s="225"/>
+      <c r="E53" s="224"/>
     </row>
     <row r="55" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B55" s="209" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E55" s="209" t="s">
         <v>308</v>
@@ -12557,8 +12557,8 @@
         <v>5</v>
       </c>
       <c r="D56" s="213"/>
-      <c r="E56" s="224" t="s">
-        <v>318</v>
+      <c r="E56" s="225" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
@@ -12569,7 +12569,7 @@
         <v>-0.15</v>
       </c>
       <c r="D57" s="214"/>
-      <c r="E57" s="225"/>
+      <c r="E57" s="224"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B58" s="138" t="s">
@@ -12583,7 +12583,7 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E58" s="225"/>
+      <c r="E58" s="224"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B59" s="138" t="s">
@@ -12594,7 +12594,7 @@
         <v>9.9999999999999922E-2</v>
       </c>
       <c r="D59" s="215"/>
-      <c r="E59" s="225"/>
+      <c r="E59" s="224"/>
     </row>
     <row r="61" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B61" s="138" t="s">
@@ -12754,13 +12754,12 @@
       <c r="E77" s="43"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
+    <mergeCell ref="E56:E59"/>
     <mergeCell ref="E50:E53"/>
     <mergeCell ref="E7:E13"/>
     <mergeCell ref="E44:E47"/>
-    <mergeCell ref="E24:E26"/>
     <mergeCell ref="E38:E41"/>
-    <mergeCell ref="E56:E59"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
